--- a/unduhan/latihan-03-kas-kecil-soal.xlsx
+++ b/unduhan/latihan-03-kas-kecil-soal.xlsx
@@ -600,7 +600,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Latihan 3 dari 24  |  Tingkat: Pemula  |  Perkiraan waktu: 40 menit  |  pushexcel.github.io/Pushexcel</t>
+          <t>Latihan 3 dari 104  |  Tingkat: Pemula  |  Perkiraan waktu: 40 menit  |  pushexcel.github.io/Pushexcel</t>
         </is>
       </c>
     </row>
